--- a/Deep-DA17/ExcelWork/Deep Assessment.xlsx
+++ b/Deep-DA17/ExcelWork/Deep Assessment.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASDC50\OneDrive\ドキュメント\My Shapes\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Library2\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE9EDBA-5343-43C0-9E59-F5708C6B3F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3AAFF97-CF78-4851-BEBD-14BBC50C3B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1A80B794-78B4-4D67-8E43-C034512DB175}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{1A80B794-78B4-4D67-8E43-C034512DB175}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$223:$B$229</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="13" r:id="rId2"/>
+    <pivotCache cacheId="17" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,8 +41,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="92">
   <si>
     <t>1. Calculate Total Sales for each order (Quantity × Unit_Price).</t>
   </si>
@@ -230,13 +259,101 @@
   </si>
   <si>
     <t>15. Use IF to classify students as Eligible (Attendance &gt;= 85%).</t>
+  </si>
+  <si>
+    <t>Total orders</t>
+  </si>
+  <si>
+    <t>Elgibilty</t>
+  </si>
+  <si>
+    <t>16. Create a Pivot Table showing Product-wise Total Sales.</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Total Sales</t>
+  </si>
+  <si>
+    <t>17. Create a Pivot Table showing Region-wise Total Sales.</t>
+  </si>
+  <si>
+    <t>18. Insert a Pivot Chart for Product-wise Sales.</t>
+  </si>
+  <si>
+    <t>19. Create a Bar Chart for Student Excel marks.</t>
+  </si>
+  <si>
+    <t>Sum of Excel</t>
+  </si>
+  <si>
+    <t>Sum of Maths</t>
+  </si>
+  <si>
+    <t>Sum of Statistics</t>
+  </si>
+  <si>
+    <t>20. Find Median of Statistics marks.</t>
+  </si>
+  <si>
+    <t>Median of Staticts</t>
+  </si>
+  <si>
+    <t>21. Find Standard Deviation of Excel marks.</t>
+  </si>
+  <si>
+    <t>Standard Deviation</t>
+  </si>
+  <si>
+    <t>22. Use CONCAT to combine Student_ID and Name.</t>
+  </si>
+  <si>
+    <t>23. Use LEFT function to extract first 2 letters of Salesperson name.</t>
+  </si>
+  <si>
+    <t>24. Apply Conditional Formatting to highlight Final Amount &gt; 60000.</t>
+  </si>
+  <si>
+    <t>25. Filter orders where Product is Laptop and Quantity &gt; 1.</t>
+  </si>
+  <si>
+    <t>26. Use COUNTIFS to count Laptop orders in North region.</t>
+  </si>
+  <si>
+    <t>27. Use ROUND to round Unit_Price to nearest thousand.</t>
+  </si>
+  <si>
+    <t>28. Remove duplicate records if present.</t>
+  </si>
+  <si>
+    <t>29. Freeze top row in Sales_Data sheet.</t>
+  </si>
+  <si>
+    <t>30. Protect the Student_Marks sheet.</t>
+  </si>
+  <si>
+    <t>GST%</t>
+  </si>
+  <si>
+    <t>Total Amount</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,17 +379,46 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -285,10 +431,2757 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Deep Assessment.xlsx]Sheet1!PivotTable4</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Product</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> wise sales</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$141</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$142:$B$145</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Laptop</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Mobile</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Tablet</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$142:$C$145</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>225000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>135000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>54000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B36E-4E62-BFAB-B752797801E8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1275057856"/>
+        <c:axId val="1186890000"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1275057856"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1186890000"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1186890000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1275057856"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Deep Assessment.xlsx]Sheet1!PivotTable7</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$171</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Excel</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$172:$A$177</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Arjun</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Pooja</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Rahul</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Sneha</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Vikas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$172:$B$177</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>58</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-42C3-4755-BE2E-4D500C720100}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$171</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Maths</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$172:$A$177</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Arjun</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Pooja</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Rahul</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Sneha</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Vikas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$172:$C$177</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>55</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-42C3-4755-BE2E-4D500C720100}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$171</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Statistics</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$172:$A$177</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Arjun</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Pooja</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Rahul</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Sneha</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Vikas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$172:$D$177</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-42C3-4755-BE2E-4D500C720100}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1288540512"/>
+        <c:axId val="1186909200"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1288540512"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1186909200"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1186909200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1288540512"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>166</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFA216C7-3063-E643-8999-CC2C8CC9E676}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>177</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>192</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5911ECBA-1933-BEE4-7346-5889D0457772}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Library2" refreshedDate="46210.686201851851" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="6" xr:uid="{9D148D38-5F22-4868-9CB5-3AF5E3C49BDA}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A2:I8" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="9">
+    <cacheField name="Order_ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="301" maxValue="306"/>
+    </cacheField>
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems count="4">
+        <s v="North"/>
+        <s v="South"/>
+        <s v="East"/>
+        <s v="West"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Salesperson" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Laptop"/>
+        <s v="Mobile"/>
+        <s v="Tablet"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Quantity" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
+    </cacheField>
+    <cacheField name="Unit_Price" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="15000" maxValue="45000"/>
+    </cacheField>
+    <cacheField name="Sales_Date" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Field8" caption="Field8" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Total Sales" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="45000" maxValue="90000"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Library2" refreshedDate="46210.689422106479" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="5" xr:uid="{6B23AB15-9E17-46EA-8E73-AA4BC1A9D482}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A127:F132" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="Student_ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
+    </cacheField>
+    <cacheField name="Name" numFmtId="0">
+      <sharedItems count="5">
+        <s v="Rahul"/>
+        <s v="Sneha"/>
+        <s v="Arjun"/>
+        <s v="Pooja"/>
+        <s v="Vikas"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Maths" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="55" maxValue="92"/>
+    </cacheField>
+    <cacheField name="Statistics" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="60" maxValue="91"/>
+    </cacheField>
+    <cacheField name="Excel" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="58" maxValue="94"/>
+    </cacheField>
+    <cacheField name="Attendance_%" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="80" maxValue="98"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="6">
+  <r>
+    <n v="301"/>
+    <x v="0"/>
+    <s v="Amit"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="45000"/>
+    <s v="05-01-2025"/>
+    <m/>
+    <n v="90000"/>
+  </r>
+  <r>
+    <n v="302"/>
+    <x v="1"/>
+    <s v="Riya"/>
+    <x v="1"/>
+    <n v="5"/>
+    <n v="15000"/>
+    <s v="07-01-2025"/>
+    <m/>
+    <n v="75000"/>
+  </r>
+  <r>
+    <n v="303"/>
+    <x v="2"/>
+    <s v="Kunal"/>
+    <x v="2"/>
+    <n v="3"/>
+    <n v="18000"/>
+    <s v="10-01-2025"/>
+    <m/>
+    <n v="54000"/>
+  </r>
+  <r>
+    <n v="304"/>
+    <x v="3"/>
+    <s v="Neha"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="45000"/>
+    <s v="12-01-2025"/>
+    <m/>
+    <n v="45000"/>
+  </r>
+  <r>
+    <n v="305"/>
+    <x v="0"/>
+    <s v="Amit"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="15000"/>
+    <s v="15-01-2025"/>
+    <m/>
+    <n v="60000"/>
+  </r>
+  <r>
+    <n v="306"/>
+    <x v="1"/>
+    <s v="Riya"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="45000"/>
+    <s v="18-01-2025"/>
+    <m/>
+    <n v="90000"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="5">
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="78"/>
+    <n v="82"/>
+    <n v="85"/>
+    <n v="92"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <n v="88"/>
+    <n v="91"/>
+    <n v="90"/>
+    <n v="96"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <n v="65"/>
+    <n v="70"/>
+    <n v="72"/>
+    <n v="85"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <n v="92"/>
+    <n v="89"/>
+    <n v="94"/>
+    <n v="98"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <n v="55"/>
+    <n v="60"/>
+    <n v="58"/>
+    <n v="80"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0EA90B73-C95F-4DE7-9F35-7DB8C80AEB49}" name="PivotTable7" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A171:D177" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Sum of Excel" fld="4" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Maths" fld="2" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Statistics" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{78AA7282-B535-4D90-AD68-946C37385961}" name="PivotTable6" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="J139:M145" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Sum of Excel" fld="4" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Maths" fld="2" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Statistics" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{14BDB1CF-36AD-45BF-98B0-15D2C20F91F6}" name="PivotTable5" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B149:C154" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7CE1BA2B-F922-46FC-AEA5-BDEF25BB8CBA}" name="PivotTable4" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="B141:C145" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -326,7 +3219,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -432,7 +3325,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -574,7 +3467,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -582,21 +3475,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692D5FAA-148C-4B9F-8603-D8EB3A3409F2}">
-  <dimension ref="A1:K125"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:M273"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
     <col min="6" max="6" width="13.140625" customWidth="1"/>
     <col min="8" max="9" width="10.42578125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -621,8 +3521,17 @@
       <c r="I2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>301</v>
       </c>
@@ -648,8 +3557,19 @@
         <f>E3*F3</f>
         <v>90000</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="K3">
+        <f>I3*J3</f>
+        <v>16200</v>
+      </c>
+      <c r="L3">
+        <f>I3+K3</f>
+        <v>106200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>302</v>
       </c>
@@ -675,8 +3595,19 @@
         <f t="shared" ref="I4:I8" si="0">E4*F4</f>
         <v>75000</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="K4">
+        <f t="shared" ref="K4:K8" si="1">I4*J4</f>
+        <v>9000</v>
+      </c>
+      <c r="L4">
+        <f t="shared" ref="L4:L8" si="2">I4+K4</f>
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>303</v>
       </c>
@@ -702,8 +3633,19 @@
         <f t="shared" si="0"/>
         <v>54000</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>6480</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="2"/>
+        <v>60480</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>304</v>
       </c>
@@ -729,8 +3671,19 @@
         <f t="shared" si="0"/>
         <v>45000</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="1"/>
+        <v>8100</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="2"/>
+        <v>53100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>305</v>
       </c>
@@ -756,8 +3709,19 @@
         <f t="shared" si="0"/>
         <v>60000</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="1"/>
+        <v>7200</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="2"/>
+        <v>67200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>306</v>
       </c>
@@ -783,13 +3747,30 @@
         <f t="shared" si="0"/>
         <v>90000</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J8" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="1"/>
+        <v>16200</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="2"/>
+        <v>106200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L9">
+        <f>SUM(L3:L8)</f>
+        <v>477180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -803,7 +3784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -813,8 +3794,12 @@
       <c r="C14">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D14">
+        <f>VLOOKUP(A14,D2:K8,8,0)</f>
+        <v>16200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -824,8 +3809,12 @@
       <c r="C15">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D15">
+        <f t="shared" ref="D15:D16" si="3">VLOOKUP(A15,D3:K9,8,0)</f>
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -835,13 +3824,17 @@
       <c r="C16">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D16">
+        <f t="shared" si="3"/>
+        <v>6480</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -855,7 +3848,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -865,9 +3858,12 @@
       <c r="C21">
         <v>18</v>
       </c>
-      <c r="D21" s="1"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D21" s="1">
+        <f>K3+J3</f>
+        <v>16200.18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -877,8 +3873,12 @@
       <c r="C22">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D22" s="1">
+        <f t="shared" ref="D22:D23" si="4">K4+J4</f>
+        <v>9000.1200000000008</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -888,13 +3888,22 @@
       <c r="C23">
         <v>12</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D23" s="1">
+        <f t="shared" si="4"/>
+        <v>6480.12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -907,43 +3916,74 @@
       <c r="D27" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="H27">
+        <f>COUNTA(A3:A8)</f>
+        <v>6</v>
+      </c>
+      <c r="I27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D28">
+        <v>477180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>3</v>
-      </c>
-      <c r="B28" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>7</v>
       </c>
       <c r="B29" t="s">
         <v>29</v>
       </c>
       <c r="C29">
+        <v>18</v>
+      </c>
+      <c r="D29">
+        <v>106200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D30">
+        <v>106200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31">
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="D31">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D32">
+        <v>67200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>11</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B33" t="s">
         <v>29</v>
       </c>
-      <c r="C30">
+      <c r="C33">
         <v>12</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>35</v>
+      <c r="D33">
+        <v>60480</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D34">
+        <v>53100</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1122,8 +4162,8 @@
         <v>1</v>
       </c>
       <c r="C46">
-        <f>F38+F42</f>
-        <v>60000</v>
+        <f>F38+E48</f>
+        <v>45000</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1131,7 +4171,7 @@
         <v>38</v>
       </c>
       <c r="C47">
-        <f t="shared" ref="C47:C49" si="1">F39+F43</f>
+        <f t="shared" ref="C47:C49" si="5">F39+F43</f>
         <v>60000</v>
       </c>
     </row>
@@ -1140,7 +4180,7 @@
         <v>39</v>
       </c>
       <c r="C48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>18000</v>
       </c>
     </row>
@@ -1149,7 +4189,7 @@
         <v>13</v>
       </c>
       <c r="C49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>45000</v>
       </c>
     </row>
@@ -1338,7 +4378,7 @@
         <v>5</v>
       </c>
       <c r="D64" t="str">
-        <f t="shared" ref="D64:D68" si="2">IF(C64&gt;=3, "high", "low")</f>
+        <f t="shared" ref="D64:D68" si="6">IF(C64&gt;=3, "high", "low")</f>
         <v>high</v>
       </c>
     </row>
@@ -1347,7 +4387,7 @@
         <v>3</v>
       </c>
       <c r="D65" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>high</v>
       </c>
     </row>
@@ -1356,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="D66" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>low</v>
       </c>
     </row>
@@ -1365,7 +4405,7 @@
         <v>4</v>
       </c>
       <c r="D67" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>high</v>
       </c>
     </row>
@@ -1374,7 +4414,7 @@
         <v>2</v>
       </c>
       <c r="D68" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>low</v>
       </c>
     </row>
@@ -1548,11 +4588,19 @@
       <c r="D80" t="s">
         <v>42</v>
       </c>
+      <c r="E80">
+        <f>MAX(I3:I8)</f>
+        <v>90000</v>
+      </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D81" t="s">
         <v>43</v>
       </c>
+      <c r="E81">
+        <f>MIN(I3:I8)</f>
+        <v>45000</v>
+      </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
@@ -1635,7 +4683,7 @@
         <v>8</v>
       </c>
       <c r="I87" t="str">
-        <f t="shared" ref="I87:I91" si="3">TEXT(G87,"mmm")</f>
+        <f t="shared" ref="I87:I91" si="7">TEXT(G87,"mmm")</f>
         <v>Jan</v>
       </c>
     </row>
@@ -1662,7 +4710,7 @@
         <v>12</v>
       </c>
       <c r="I88" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Jan</v>
       </c>
     </row>
@@ -1689,7 +4737,7 @@
         <v>15</v>
       </c>
       <c r="I89" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Jan</v>
       </c>
     </row>
@@ -1716,7 +4764,7 @@
         <v>16</v>
       </c>
       <c r="I90" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Jan</v>
       </c>
     </row>
@@ -1743,7 +4791,7 @@
         <v>17</v>
       </c>
       <c r="I91" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Jan</v>
       </c>
     </row>
@@ -1752,151 +4800,151 @@
         <v>46</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>47</v>
       </c>
     </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>48</v>
+      </c>
+      <c r="B98" t="s">
+        <v>49</v>
+      </c>
+      <c r="C98" t="s">
+        <v>50</v>
+      </c>
+      <c r="D98" t="s">
+        <v>51</v>
+      </c>
+      <c r="E98" t="s">
+        <v>52</v>
+      </c>
+      <c r="F98" t="s">
+        <v>53</v>
+      </c>
+      <c r="H98" t="s">
+        <v>59</v>
+      </c>
+    </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>48</v>
+      <c r="A99">
+        <v>1</v>
       </c>
       <c r="B99" t="s">
-        <v>49</v>
-      </c>
-      <c r="C99" t="s">
-        <v>50</v>
-      </c>
-      <c r="D99" t="s">
-        <v>51</v>
-      </c>
-      <c r="E99" t="s">
-        <v>52</v>
-      </c>
-      <c r="F99" t="s">
-        <v>53</v>
-      </c>
-      <c r="H99" t="s">
-        <v>59</v>
+        <v>54</v>
+      </c>
+      <c r="C99">
+        <v>78</v>
+      </c>
+      <c r="D99">
+        <v>82</v>
+      </c>
+      <c r="E99">
+        <v>85</v>
+      </c>
+      <c r="F99">
+        <v>92</v>
+      </c>
+      <c r="H99">
+        <f>AVERAGE(C99,D99,E99)</f>
+        <v>81.666666666666671</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B100" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C100">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D100">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E100">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F100">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H100">
-        <f>AVERAGE(C100,D100,E100)</f>
-        <v>81.666666666666671</v>
+        <f t="shared" ref="H100:H103" si="8">AVERAGE(C100,D100,E100)</f>
+        <v>89.666666666666671</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B101" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C101">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="D101">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="E101">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F101">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H101">
-        <f t="shared" ref="H101:H104" si="4">AVERAGE(C101,D101,E101)</f>
-        <v>89.666666666666671</v>
+        <f t="shared" si="8"/>
+        <v>69</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B102" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C102">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="D102">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="E102">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="F102">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="H102">
-        <f t="shared" si="4"/>
-        <v>69</v>
+        <f t="shared" si="8"/>
+        <v>91.666666666666671</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B103" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C103">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="D103">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="E103">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="F103">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="H103">
-        <f t="shared" si="4"/>
-        <v>91.666666666666671</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>5</v>
-      </c>
-      <c r="B104" t="s">
-        <v>58</v>
-      </c>
-      <c r="C104">
-        <v>55</v>
-      </c>
-      <c r="D104">
-        <v>60</v>
-      </c>
-      <c r="E104">
-        <v>58</v>
-      </c>
-      <c r="F104">
-        <v>80</v>
-      </c>
-      <c r="H104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>57.666666666666664</v>
       </c>
     </row>
@@ -1982,7 +5030,7 @@
         <v>96</v>
       </c>
       <c r="H111">
-        <f t="shared" ref="H111:H114" si="5">AVERAGE(C111,D111,E111)</f>
+        <f t="shared" ref="H111:H114" si="9">AVERAGE(C111,D111,E111)</f>
         <v>89.666666666666671</v>
       </c>
     </row>
@@ -2006,7 +5054,7 @@
         <v>85</v>
       </c>
       <c r="H112">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>69</v>
       </c>
     </row>
@@ -2030,7 +5078,7 @@
         <v>98</v>
       </c>
       <c r="H113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>91.666666666666671</v>
       </c>
     </row>
@@ -2054,7 +5102,7 @@
         <v>80</v>
       </c>
       <c r="H114">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>57.666666666666664</v>
       </c>
     </row>
@@ -2140,7 +5188,7 @@
         <v>96</v>
       </c>
       <c r="H120">
-        <f t="shared" ref="H120:H123" si="6">AVERAGE(C120,D120,E120)</f>
+        <f t="shared" ref="H120:H123" si="10">AVERAGE(C120,D120,E120)</f>
         <v>89.666666666666671</v>
       </c>
     </row>
@@ -2164,7 +5212,7 @@
         <v>85</v>
       </c>
       <c r="H121">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>69</v>
       </c>
     </row>
@@ -2188,7 +5236,7 @@
         <v>98</v>
       </c>
       <c r="H122">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>91.666666666666671</v>
       </c>
     </row>
@@ -2212,7 +5260,7 @@
         <v>80</v>
       </c>
       <c r="H123">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>57.666666666666664</v>
       </c>
     </row>
@@ -2221,7 +5269,1133 @@
         <v>64</v>
       </c>
     </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>48</v>
+      </c>
+      <c r="B127" t="s">
+        <v>49</v>
+      </c>
+      <c r="C127" t="s">
+        <v>50</v>
+      </c>
+      <c r="D127" t="s">
+        <v>51</v>
+      </c>
+      <c r="E127" t="s">
+        <v>52</v>
+      </c>
+      <c r="F127" t="s">
+        <v>53</v>
+      </c>
+      <c r="H127" t="s">
+        <v>59</v>
+      </c>
+      <c r="I127" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>1</v>
+      </c>
+      <c r="B128" t="s">
+        <v>54</v>
+      </c>
+      <c r="C128">
+        <v>78</v>
+      </c>
+      <c r="D128">
+        <v>82</v>
+      </c>
+      <c r="E128">
+        <v>85</v>
+      </c>
+      <c r="F128">
+        <v>92</v>
+      </c>
+      <c r="H128">
+        <f>AVERAGE(C128,D128,E128)</f>
+        <v>81.666666666666671</v>
+      </c>
+      <c r="I128" t="str">
+        <f>IF(F128&gt;=85, "Eligible", "Not Eligible")</f>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>2</v>
+      </c>
+      <c r="B129" t="s">
+        <v>55</v>
+      </c>
+      <c r="C129">
+        <v>88</v>
+      </c>
+      <c r="D129">
+        <v>91</v>
+      </c>
+      <c r="E129">
+        <v>90</v>
+      </c>
+      <c r="F129">
+        <v>96</v>
+      </c>
+      <c r="H129">
+        <f t="shared" ref="H129:H132" si="11">AVERAGE(C129,D129,E129)</f>
+        <v>89.666666666666671</v>
+      </c>
+      <c r="I129" t="str">
+        <f t="shared" ref="I129:I132" si="12">IF(F129&gt;=85, "Eligible", "Not Eligible")</f>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>3</v>
+      </c>
+      <c r="B130" t="s">
+        <v>56</v>
+      </c>
+      <c r="C130">
+        <v>65</v>
+      </c>
+      <c r="D130">
+        <v>70</v>
+      </c>
+      <c r="E130">
+        <v>72</v>
+      </c>
+      <c r="F130">
+        <v>85</v>
+      </c>
+      <c r="H130">
+        <f t="shared" si="11"/>
+        <v>69</v>
+      </c>
+      <c r="I130" t="str">
+        <f t="shared" si="12"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>4</v>
+      </c>
+      <c r="B131" t="s">
+        <v>57</v>
+      </c>
+      <c r="C131">
+        <v>92</v>
+      </c>
+      <c r="D131">
+        <v>89</v>
+      </c>
+      <c r="E131">
+        <v>94</v>
+      </c>
+      <c r="F131">
+        <v>98</v>
+      </c>
+      <c r="H131">
+        <f t="shared" si="11"/>
+        <v>91.666666666666671</v>
+      </c>
+      <c r="I131" t="str">
+        <f t="shared" si="12"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>5</v>
+      </c>
+      <c r="B132" t="s">
+        <v>58</v>
+      </c>
+      <c r="C132">
+        <v>55</v>
+      </c>
+      <c r="D132">
+        <v>60</v>
+      </c>
+      <c r="E132">
+        <v>58</v>
+      </c>
+      <c r="F132">
+        <v>80</v>
+      </c>
+      <c r="H132">
+        <f t="shared" si="11"/>
+        <v>57.666666666666664</v>
+      </c>
+      <c r="I132" t="str">
+        <f t="shared" si="12"/>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>21</v>
+      </c>
+      <c r="B136" t="s">
+        <v>27</v>
+      </c>
+      <c r="C136" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>3</v>
+      </c>
+      <c r="B137" t="s">
+        <v>29</v>
+      </c>
+      <c r="C137">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>7</v>
+      </c>
+      <c r="B138" t="s">
+        <v>29</v>
+      </c>
+      <c r="C138">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>11</v>
+      </c>
+      <c r="B139" t="s">
+        <v>29</v>
+      </c>
+      <c r="C139">
+        <v>12</v>
+      </c>
+      <c r="J139" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K139" t="s">
+        <v>74</v>
+      </c>
+      <c r="L139" t="s">
+        <v>75</v>
+      </c>
+      <c r="M139" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J140" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K140" s="4">
+        <v>72</v>
+      </c>
+      <c r="L140" s="4">
+        <v>65</v>
+      </c>
+      <c r="M140" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B141" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C141" t="s">
+        <v>70</v>
+      </c>
+      <c r="J141" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K141" s="4">
+        <v>94</v>
+      </c>
+      <c r="L141" s="4">
+        <v>92</v>
+      </c>
+      <c r="M141" s="4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B142" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C142" s="4">
+        <v>225000</v>
+      </c>
+      <c r="J142" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K142" s="4">
+        <v>85</v>
+      </c>
+      <c r="L142" s="4">
+        <v>78</v>
+      </c>
+      <c r="M142" s="4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B143" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C143" s="4">
+        <v>135000</v>
+      </c>
+      <c r="J143" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K143" s="4">
+        <v>90</v>
+      </c>
+      <c r="L143" s="4">
+        <v>88</v>
+      </c>
+      <c r="M143" s="4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B144" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144" s="4">
+        <v>54000</v>
+      </c>
+      <c r="J144" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K144" s="4">
+        <v>58</v>
+      </c>
+      <c r="L144" s="4">
+        <v>55</v>
+      </c>
+      <c r="M144" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B145" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C145" s="4">
+        <v>414000</v>
+      </c>
+      <c r="J145" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K145" s="4">
+        <v>399</v>
+      </c>
+      <c r="L145" s="4">
+        <v>378</v>
+      </c>
+      <c r="M145" s="4">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B149" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C149" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B150" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C150" s="4">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B151" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C151" s="4">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B152" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C152" s="4">
+        <v>165000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B153" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C153" s="4">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B154" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C154" s="4">
+        <v>414000</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C171" t="s">
+        <v>75</v>
+      </c>
+      <c r="D171" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B172" s="4">
+        <v>72</v>
+      </c>
+      <c r="C172" s="4">
+        <v>65</v>
+      </c>
+      <c r="D172" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B173" s="4">
+        <v>94</v>
+      </c>
+      <c r="C173" s="4">
+        <v>92</v>
+      </c>
+      <c r="D173" s="4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B174" s="4">
+        <v>85</v>
+      </c>
+      <c r="C174" s="4">
+        <v>78</v>
+      </c>
+      <c r="D174" s="4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B175" s="4">
+        <v>90</v>
+      </c>
+      <c r="C175" s="4">
+        <v>88</v>
+      </c>
+      <c r="D175" s="4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B176" s="4">
+        <v>58</v>
+      </c>
+      <c r="C176" s="4">
+        <v>55</v>
+      </c>
+      <c r="D176" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B177" s="4">
+        <v>399</v>
+      </c>
+      <c r="C177" s="4">
+        <v>378</v>
+      </c>
+      <c r="D177" s="4">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <f>MEDIAN(D172:D176)</f>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <f>_xlfn.STDEV.S(B172:B176)</f>
+        <v>14.737706741552426</v>
+      </c>
+      <c r="B201" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" t="str">
+        <f>_xlfn.CONCAT(A110,B110)</f>
+        <v>1Rahul</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" t="str">
+        <f>LEFT(C86,2)</f>
+        <v>Am</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>21</v>
+      </c>
+      <c r="B223" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>3</v>
+      </c>
+      <c r="B224">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>7</v>
+      </c>
+      <c r="B225">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>11</v>
+      </c>
+      <c r="B226">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>3</v>
+      </c>
+      <c r="B227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>7</v>
+      </c>
+      <c r="B228">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>3</v>
+      </c>
+      <c r="B229">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>3</v>
+      </c>
+      <c r="B234">
+        <f>COUNTIF(B2:I8, "North")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>45000</v>
+      </c>
+      <c r="B238" cm="1">
+        <f t="array" ref="B238:B243">ROUND(A238:A243, 0)</f>
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>15000</v>
+      </c>
+      <c r="B239">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>18000</v>
+      </c>
+      <c r="B240">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>45000</v>
+      </c>
+      <c r="B241">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>15000</v>
+      </c>
+      <c r="B242">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>45000</v>
+      </c>
+      <c r="B243">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>18</v>
+      </c>
+      <c r="C248" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>301</v>
+      </c>
+      <c r="C249" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>302</v>
+      </c>
+      <c r="C250" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>303</v>
+      </c>
+      <c r="C251" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>304</v>
+      </c>
+      <c r="C252" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>18</v>
+      </c>
+      <c r="B258" t="s">
+        <v>19</v>
+      </c>
+      <c r="C258" t="s">
+        <v>20</v>
+      </c>
+      <c r="D258" t="s">
+        <v>21</v>
+      </c>
+      <c r="E258" t="s">
+        <v>22</v>
+      </c>
+      <c r="F258" t="s">
+        <v>23</v>
+      </c>
+      <c r="G258" t="s">
+        <v>24</v>
+      </c>
+      <c r="I258" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>301</v>
+      </c>
+      <c r="B259" t="s">
+        <v>1</v>
+      </c>
+      <c r="C259" t="s">
+        <v>2</v>
+      </c>
+      <c r="D259" t="s">
+        <v>3</v>
+      </c>
+      <c r="E259">
+        <v>2</v>
+      </c>
+      <c r="F259">
+        <v>45000</v>
+      </c>
+      <c r="G259" t="s">
+        <v>4</v>
+      </c>
+      <c r="I259" t="str">
+        <f>TEXT(H259,"mmm")</f>
+        <v>Jan</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>302</v>
+      </c>
+      <c r="B260" t="s">
+        <v>5</v>
+      </c>
+      <c r="C260" t="s">
+        <v>6</v>
+      </c>
+      <c r="D260" t="s">
+        <v>7</v>
+      </c>
+      <c r="E260">
+        <v>5</v>
+      </c>
+      <c r="F260">
+        <v>15000</v>
+      </c>
+      <c r="G260" t="s">
+        <v>8</v>
+      </c>
+      <c r="I260" t="str">
+        <f t="shared" ref="I260:I264" si="13">TEXT(G260,"mmm")</f>
+        <v>Jan</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>303</v>
+      </c>
+      <c r="B261" t="s">
+        <v>9</v>
+      </c>
+      <c r="C261" t="s">
+        <v>10</v>
+      </c>
+      <c r="D261" t="s">
+        <v>11</v>
+      </c>
+      <c r="E261">
+        <v>3</v>
+      </c>
+      <c r="F261">
+        <v>18000</v>
+      </c>
+      <c r="G261" t="s">
+        <v>12</v>
+      </c>
+      <c r="I261" t="str">
+        <f t="shared" si="13"/>
+        <v>Jan</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>304</v>
+      </c>
+      <c r="B262" t="s">
+        <v>13</v>
+      </c>
+      <c r="C262" t="s">
+        <v>14</v>
+      </c>
+      <c r="D262" t="s">
+        <v>3</v>
+      </c>
+      <c r="E262">
+        <v>1</v>
+      </c>
+      <c r="F262">
+        <v>45000</v>
+      </c>
+      <c r="G262" t="s">
+        <v>15</v>
+      </c>
+      <c r="I262" t="str">
+        <f t="shared" si="13"/>
+        <v>Jan</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>305</v>
+      </c>
+      <c r="B263" t="s">
+        <v>1</v>
+      </c>
+      <c r="C263" t="s">
+        <v>2</v>
+      </c>
+      <c r="D263" t="s">
+        <v>7</v>
+      </c>
+      <c r="E263">
+        <v>4</v>
+      </c>
+      <c r="F263">
+        <v>15000</v>
+      </c>
+      <c r="G263" t="s">
+        <v>16</v>
+      </c>
+      <c r="I263" t="str">
+        <f t="shared" si="13"/>
+        <v>Jan</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>306</v>
+      </c>
+      <c r="B264" t="s">
+        <v>5</v>
+      </c>
+      <c r="C264" t="s">
+        <v>6</v>
+      </c>
+      <c r="D264" t="s">
+        <v>3</v>
+      </c>
+      <c r="E264">
+        <v>2</v>
+      </c>
+      <c r="F264">
+        <v>45000</v>
+      </c>
+      <c r="G264" t="s">
+        <v>17</v>
+      </c>
+      <c r="I264" t="str">
+        <f t="shared" si="13"/>
+        <v>Jan</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>48</v>
+      </c>
+      <c r="B268" t="s">
+        <v>49</v>
+      </c>
+      <c r="C268" t="s">
+        <v>50</v>
+      </c>
+      <c r="D268" t="s">
+        <v>51</v>
+      </c>
+      <c r="E268" t="s">
+        <v>52</v>
+      </c>
+      <c r="F268" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>1</v>
+      </c>
+      <c r="B269" t="s">
+        <v>54</v>
+      </c>
+      <c r="C269">
+        <v>78</v>
+      </c>
+      <c r="D269">
+        <v>82</v>
+      </c>
+      <c r="E269">
+        <v>85</v>
+      </c>
+      <c r="F269">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>2</v>
+      </c>
+      <c r="B270" t="s">
+        <v>55</v>
+      </c>
+      <c r="C270">
+        <v>88</v>
+      </c>
+      <c r="D270">
+        <v>91</v>
+      </c>
+      <c r="E270">
+        <v>90</v>
+      </c>
+      <c r="F270">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>3</v>
+      </c>
+      <c r="B271" t="s">
+        <v>56</v>
+      </c>
+      <c r="C271">
+        <v>65</v>
+      </c>
+      <c r="D271">
+        <v>70</v>
+      </c>
+      <c r="E271">
+        <v>72</v>
+      </c>
+      <c r="F271">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>4</v>
+      </c>
+      <c r="B272" t="s">
+        <v>57</v>
+      </c>
+      <c r="C272">
+        <v>92</v>
+      </c>
+      <c r="D272">
+        <v>89</v>
+      </c>
+      <c r="E272">
+        <v>94</v>
+      </c>
+      <c r="F272">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>5</v>
+      </c>
+      <c r="B273" t="s">
+        <v>58</v>
+      </c>
+      <c r="C273">
+        <v>55</v>
+      </c>
+      <c r="D273">
+        <v>60</v>
+      </c>
+      <c r="E273">
+        <v>58</v>
+      </c>
+      <c r="F273">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="et0Ge7AyYfN1qzbeUug/ZVCFtDXTrItyGsaZMlKzSqYeIrr/JtvhDrMVhUF6lllmt/lDtuqBBM/kZPs65L2ZMA==" saltValue="9rZulWRRAWzxCETVVDNBCQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <autoFilter ref="A223:B229" xr:uid="{692D5FAA-148C-4B9F-8603-D8EB3A3409F2}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Laptop"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A28:D34">
+    <sortCondition descending="1" ref="D28:D34"/>
+  </sortState>
+  <conditionalFormatting sqref="A214:A220">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>60000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C248:C252">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>